--- a/excel/MediaCatalog_template.xlsx
+++ b/excel/MediaCatalog_template.xlsx
@@ -510,12 +510,12 @@
       </c>
       <c r="C1" s="8" t="inlineStr">
         <is>
-          <t>Blu-ray.com URL</t>
+          <t>Blu-ray URL</t>
         </is>
       </c>
       <c r="D1" s="8" t="inlineStr">
         <is>
-          <t>Blu-ray.com Title</t>
+          <t>Blu-ray Title</t>
         </is>
       </c>
       <c r="E1" s="8" t="inlineStr">
